--- a/Assets/LingBoCanteen/Datatables/Excel/Ingredient.xlsx
+++ b/Assets/LingBoCanteen/Datatables/Excel/Ingredient.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\project\GoldenDolphin\GoldenDolphin\GoldenDolphinGame\Assets\LingBoCanteen\Datatables\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C63299D6DDFD7B82D3FA39772278A89A85582C8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18052" windowHeight="8655"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -512,14 +518,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -528,345 +528,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -874,257 +550,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1132,61 +563,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1444,496 +831,496 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1327433628319" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="20.3185840707965" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5309734513274" customWidth="1"/>
-    <col min="7" max="7" width="19.070796460177" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.3274336283186" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.2035398230088" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.7964601769912" customWidth="1"/>
-    <col min="11" max="11" width="12.1327433628319" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.6017699115044" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="20.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="19.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.75" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.58203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
         <v>1001</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="E5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>3001</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>1002</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="E6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>3002</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
         <v>1003</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="E7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>3003</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
         <v>1004</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>3004</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
         <v>1005</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="E9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>3005</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
         <v>1006</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="E10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>3006</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
         <v>1007</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="E11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>3007</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
         <v>1008</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="E12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>3008</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
         <v>1009</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="E13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>3009</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
         <v>1010</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="s">
+      <c r="E14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>3010</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
-      <c r="B15" s="2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
         <v>1011</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E15" t="b">
@@ -1942,27 +1329,27 @@
       <c r="F15" t="b">
         <v>0</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>3011</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="B16" s="2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
         <v>1012</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E16" t="b">
@@ -1971,30 +1358,30 @@
       <c r="F16" t="b">
         <v>0</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>3012</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
-      <c r="B17" s="2">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
         <v>1013</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E17" t="b">
@@ -2003,27 +1390,27 @@
       <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>3013</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
-      <c r="B18" s="2">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
         <v>1014</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E18" t="b">
@@ -2032,33 +1419,33 @@
       <c r="F18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>3014</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="2">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
         <v>1015</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E19" t="b">
@@ -2067,30 +1454,30 @@
       <c r="F19" t="b">
         <v>0</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>3015</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
-      <c r="B20" s="2">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
         <v>1016</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E20" t="b">
@@ -2099,30 +1486,30 @@
       <c r="F20" t="b">
         <v>0</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>3016</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
-      <c r="B21" s="2">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
         <v>1017</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E21" t="b">
@@ -2131,27 +1518,27 @@
       <c r="F21" t="b">
         <v>0</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>3017</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K21" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
-      <c r="B22" s="2">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="1">
         <v>1018</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>112</v>
       </c>
       <c r="E22" t="b">
@@ -2160,27 +1547,27 @@
       <c r="F22" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>3018</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
-      <c r="B23" s="2">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="1">
         <v>1019</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>117</v>
       </c>
       <c r="E23" t="b">
@@ -2189,27 +1576,27 @@
       <c r="F23" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <v>3019</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
-      <c r="B24" s="2">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="1">
         <v>1020</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>122</v>
       </c>
       <c r="E24" t="b">
@@ -2218,27 +1605,27 @@
       <c r="F24" t="b">
         <v>0</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>3020</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
-      <c r="B25" s="2">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="1">
         <v>1021</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>127</v>
       </c>
       <c r="E25" t="b">
@@ -2247,30 +1634,30 @@
       <c r="F25" t="b">
         <v>1</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>3021</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="K25" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="2:12">
-      <c r="B26" s="2">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="1">
         <v>1022</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>133</v>
       </c>
       <c r="E26" t="b">
@@ -2279,21 +1666,21 @@
       <c r="F26" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="1">
         <v>3022</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="K26" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="2:12">
-      <c r="B27" s="2">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="1">
         <v>1023</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>136</v>
       </c>
       <c r="E27" t="b">
@@ -2302,136 +1689,136 @@
       <c r="F27" t="b">
         <v>0</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
         <v>3023</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K27" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="1">
         <v>4001</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="1">
         <v>4002</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <v>4003</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="1">
         <v>4004</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="2:12">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <v>4005</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="1">
         <v>4006</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="1">
         <v>5001</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="1">
         <v>5002</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <v>5003</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="1">
         <v>5004</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="1">
         <v>5005</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>159</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/LingBoCanteen/Datatables/Excel/Ingredient.xlsx
+++ b/Assets/LingBoCanteen/Datatables/Excel/Ingredient.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\project\GoldenDolphin\GoldenDolphin\GoldenDolphinGame\Assets\LingBoCanteen\Datatables\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_C63299D6DDFD7B82D3FA39772278A89A85582C8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18052" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="162">
   <si>
     <t>#</t>
   </si>
@@ -437,6 +431,9 @@
     <t>Flour</t>
   </si>
   <si>
+    <t>Flour_Output</t>
+  </si>
+  <si>
     <t>面团</t>
   </si>
   <si>
@@ -444,6 +441,9 @@
   </si>
   <si>
     <t>Egg</t>
+  </si>
+  <si>
+    <t>Egg_Output</t>
   </si>
   <si>
     <t>鸡蛋液</t>
@@ -518,8 +518,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -528,21 +534,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -550,9 +880,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -563,17 +1135,61 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -831,28 +1447,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1681415929204" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="20.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="19.08203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.1640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.75" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.3362831858407" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5044247787611" customWidth="1"/>
+    <col min="7" max="7" width="19.0796460176991" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.3362831858407" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1681415929204" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7522123893805" customWidth="1"/>
+    <col min="11" max="11" width="12.1681415929204" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5840707964602" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -863,7 +1479,7 @@
       <c r="F1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -901,7 +1517,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -939,7 +1555,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -977,7 +1593,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
@@ -1013,7 +1629,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
@@ -1046,7 +1662,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
@@ -1082,7 +1698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>1004</v>
@@ -1115,7 +1731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>1005</v>
@@ -1148,7 +1764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>1006</v>
@@ -1181,7 +1797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>1007</v>
@@ -1214,7 +1830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1008</v>
@@ -1247,7 +1863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
@@ -1283,7 +1899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
@@ -1313,7 +1929,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12">
       <c r="B15" s="1">
         <v>1011</v>
       </c>
@@ -1342,7 +1958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12">
       <c r="B16" s="1">
         <v>1012</v>
       </c>
@@ -1374,7 +1990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12">
       <c r="B17" s="1">
         <v>1013</v>
       </c>
@@ -1403,7 +2019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12">
       <c r="B18" s="1">
         <v>1014</v>
       </c>
@@ -1438,7 +2054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12">
       <c r="B19" s="1">
         <v>1015</v>
       </c>
@@ -1470,7 +2086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12">
       <c r="B20" s="1">
         <v>1016</v>
       </c>
@@ -1502,7 +2118,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12">
       <c r="B21" s="1">
         <v>1017</v>
       </c>
@@ -1531,7 +2147,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12">
       <c r="B22" s="1">
         <v>1018</v>
       </c>
@@ -1560,7 +2176,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12">
       <c r="B23" s="1">
         <v>1019</v>
       </c>
@@ -1589,7 +2205,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12">
       <c r="B24" s="1">
         <v>1020</v>
       </c>
@@ -1618,7 +2234,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12">
       <c r="B25" s="1">
         <v>1021</v>
       </c>
@@ -1650,7 +2266,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12">
       <c r="B26" s="1">
         <v>1022</v>
       </c>
@@ -1666,159 +2282,165 @@
       <c r="F26" t="b">
         <v>0</v>
       </c>
+      <c r="I26" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="J26" s="1">
         <v>3022</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12">
       <c r="B27" s="1">
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="J27" s="1">
         <v>3023</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
       <c r="B28" s="1">
         <v>4001</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12">
       <c r="B29" s="1">
         <v>4002</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12">
       <c r="B30" s="1">
         <v>4003</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12">
       <c r="B31" s="1">
         <v>4004</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12">
       <c r="B32" s="1">
         <v>4005</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
       <c r="B33" s="1">
         <v>4006</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
       <c r="B34" s="1">
         <v>5001</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
       <c r="B35" s="1">
         <v>5002</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
       <c r="B36" s="1">
         <v>5003</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
       <c r="B37" s="1">
         <v>5004</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
       <c r="B38" s="1">
         <v>5005</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/LingBoCanteen/Datatables/Excel/Ingredient.xlsx
+++ b/Assets/LingBoCanteen/Datatables/Excel/Ingredient.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\project\GoldenDolphin\GoldenDolphin\GoldenDolphinGame\Assets\LingBoCanteen\DataTables\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF71EDB-3DBB-45B3-9F99-3D55D6AE1C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18052" windowHeight="8655"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="146">
   <si>
     <t>#</t>
   </si>
@@ -449,83 +453,35 @@
     <t>鸡蛋液</t>
   </si>
   <si>
-    <t>油</t>
-  </si>
-  <si>
-    <t>Seasoning_Oil</t>
-  </si>
-  <si>
-    <t>调味酱汁</t>
-  </si>
-  <si>
-    <t>Seasoning_Sauce</t>
-  </si>
-  <si>
-    <t>奶油</t>
-  </si>
-  <si>
-    <t>Seasoning_Cream</t>
-  </si>
-  <si>
-    <t>火山盐</t>
-  </si>
-  <si>
-    <t>Seasoning_Salt</t>
-  </si>
-  <si>
-    <t>糖</t>
-  </si>
-  <si>
-    <t>Seasoning_Sugar</t>
-  </si>
-  <si>
-    <t>黑胡椒</t>
-  </si>
-  <si>
-    <t>Seasoning_BlackPepper</t>
-  </si>
-  <si>
-    <t>炒锅</t>
-  </si>
-  <si>
-    <t>Pot_Wok</t>
-  </si>
-  <si>
-    <t>蒸锅</t>
-  </si>
-  <si>
-    <t>Pot_Steamer</t>
-  </si>
-  <si>
-    <t>高压锅</t>
-  </si>
-  <si>
-    <t>Pot_PresPot</t>
-  </si>
-  <si>
-    <t>汤锅</t>
-  </si>
-  <si>
-    <t>Pot_SoupPot</t>
-  </si>
-  <si>
-    <t>烤箱</t>
-  </si>
-  <si>
-    <t>Oven</t>
+    <t>MoveAssetName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动产物资源名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Apple_Moveable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lemon_Moveable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Patato_Moveable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tamoto_Moveable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -534,345 +490,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -880,253 +521,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1134,62 +533,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1447,28 +805,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.1681415929204" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="20.3362831858407" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5044247787611" customWidth="1"/>
-    <col min="7" max="7" width="19.0796460176991" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3362831858407" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.1681415929204" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7522123893805" customWidth="1"/>
-    <col min="11" max="11" width="12.1681415929204" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5840707964602" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.08203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.1640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.75" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.58203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1477,9 +836,9 @@
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1498,26 +857,29 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1546,16 +908,19 @@
         <v>14</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1574,26 +939,29 @@
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
@@ -1610,26 +978,26 @@
       <c r="F5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>3001</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
@@ -1646,23 +1014,23 @@
       <c r="F6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>3002</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
@@ -1679,26 +1047,29 @@
       <c r="F7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>3003</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>1004</v>
@@ -1715,23 +1086,23 @@
       <c r="F8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>3004</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>1005</v>
@@ -1748,23 +1119,23 @@
       <c r="F9" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>3005</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>1006</v>
@@ -1781,23 +1152,23 @@
       <c r="F10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>3006</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>1007</v>
@@ -1814,23 +1185,23 @@
       <c r="F11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>3007</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1008</v>
@@ -1847,23 +1218,23 @@
       <c r="F12" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>3008</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
@@ -1880,26 +1251,29 @@
       <c r="F13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>3009</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
@@ -1916,20 +1290,20 @@
       <c r="F14" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>3010</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>1011</v>
       </c>
@@ -1945,20 +1319,20 @@
       <c r="F15" t="b">
         <v>0</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>3011</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>1012</v>
       </c>
@@ -1974,23 +1348,26 @@
       <c r="F16" t="b">
         <v>0</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>3012</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M16" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>1013</v>
       </c>
@@ -2006,20 +1383,20 @@
       <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>3013</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>1014</v>
       </c>
@@ -2035,26 +1412,26 @@
       <c r="F18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>3014</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L18" s="1">
+      <c r="M18" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>1015</v>
       </c>
@@ -2070,23 +1447,26 @@
       <c r="F19" t="b">
         <v>0</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>3015</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L19" s="1">
+      <c r="M19" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>1016</v>
       </c>
@@ -2102,23 +1482,23 @@
       <c r="F20" t="b">
         <v>0</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>3016</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L20" s="1">
+      <c r="M20" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>1017</v>
       </c>
@@ -2134,20 +1514,20 @@
       <c r="F21" t="b">
         <v>0</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>3017</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>1018</v>
       </c>
@@ -2163,20 +1543,20 @@
       <c r="F22" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>3018</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>1019</v>
       </c>
@@ -2192,20 +1572,20 @@
       <c r="F23" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>3019</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>1020</v>
       </c>
@@ -2221,20 +1601,20 @@
       <c r="F24" t="b">
         <v>0</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>3020</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
         <v>1021</v>
       </c>
@@ -2250,23 +1630,23 @@
       <c r="F25" t="b">
         <v>1</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>3021</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="2:12">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <v>1022</v>
       </c>
@@ -2282,17 +1662,17 @@
       <c r="F26" t="b">
         <v>0</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>3022</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="2:12">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <v>1023</v>
       </c>
@@ -2308,139 +1688,18 @@
       <c r="F27" t="b">
         <v>0</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>3023</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
-      <c r="B28" s="1">
-        <v>4001</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12">
-      <c r="B29" s="1">
-        <v>4002</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12">
-      <c r="B30" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12">
-      <c r="B31" s="1">
-        <v>4004</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12">
-      <c r="B32" s="1">
-        <v>4005</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" s="1">
-        <v>4006</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="1">
-        <v>5001</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="1">
-        <v>5002</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="1">
-        <v>5003</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" s="1">
-        <v>5004</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" s="1">
-        <v>5005</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>